--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/2.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/2.xlsx
@@ -426,13 +426,13 @@
         <v>-4.075277479866347</v>
       </c>
       <c r="E2">
-        <v>-8.015804368742428</v>
+        <v>-9.96797566665351</v>
       </c>
       <c r="F2">
-        <v>-0.6921069108583143</v>
+        <v>-1.488558145995358</v>
       </c>
       <c r="G2">
-        <v>-9.31242750940984</v>
+        <v>-11.39462424730765</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.634716675474872</v>
       </c>
       <c r="E3">
-        <v>-8.82140276941942</v>
+        <v>-10.40834896984773</v>
       </c>
       <c r="F3">
-        <v>-0.6956688906903522</v>
+        <v>-1.532143525261056</v>
       </c>
       <c r="G3">
-        <v>-9.056731184156206</v>
+        <v>-11.1191919983175</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.223002374195506</v>
       </c>
       <c r="E4">
-        <v>-8.507129268469644</v>
+        <v>-11.56367683655456</v>
       </c>
       <c r="F4">
-        <v>-0.7621180386407201</v>
+        <v>-1.18851270392514</v>
       </c>
       <c r="G4">
-        <v>-8.935781914111406</v>
+        <v>-10.85823110659588</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.741961887487063</v>
       </c>
       <c r="E5">
-        <v>-9.864456874382158</v>
+        <v>-12.17919936773945</v>
       </c>
       <c r="F5">
-        <v>-0.07981748834425412</v>
+        <v>-1.418949604770712</v>
       </c>
       <c r="G5">
-        <v>-9.122007631167811</v>
+        <v>-10.87370368441511</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.183318052316757</v>
       </c>
       <c r="E6">
-        <v>-11.40188433618454</v>
+        <v>-12.89586090110656</v>
       </c>
       <c r="F6">
-        <v>-0.6099775963403545</v>
+        <v>-1.233461575935847</v>
       </c>
       <c r="G6">
-        <v>-8.655329203272538</v>
+        <v>-10.32633105732542</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.515429893045607</v>
       </c>
       <c r="E7">
-        <v>-10.90571263884125</v>
+        <v>-12.78850038835975</v>
       </c>
       <c r="F7">
-        <v>0.00421872793495013</v>
+        <v>-0.952268119218541</v>
       </c>
       <c r="G7">
-        <v>-9.149051029014858</v>
+        <v>-10.47164249052219</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.723034093406454</v>
       </c>
       <c r="E8">
-        <v>-12.73751141292482</v>
+        <v>-14.45295797174333</v>
       </c>
       <c r="F8">
-        <v>-0.3158127344626109</v>
+        <v>-0.9740193904812504</v>
       </c>
       <c r="G8">
-        <v>-8.310555577942413</v>
+        <v>-10.26800441241535</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.797221959891586</v>
       </c>
       <c r="E9">
-        <v>-14.05671253887541</v>
+        <v>-14.51896911254016</v>
       </c>
       <c r="F9">
-        <v>-0.007506812651676872</v>
+        <v>-0.8811792854450931</v>
       </c>
       <c r="G9">
-        <v>-8.630459250297593</v>
+        <v>-10.33431340891274</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.735562584966836</v>
       </c>
       <c r="E10">
-        <v>-12.02659377081995</v>
+        <v>-14.73431311973252</v>
       </c>
       <c r="F10">
-        <v>0.3383307794452971</v>
+        <v>-0.7059041983193428</v>
       </c>
       <c r="G10">
-        <v>-8.479953740736798</v>
+        <v>-9.316102132421832</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.549042806044764</v>
       </c>
       <c r="E11">
-        <v>-14.71767535516525</v>
+        <v>-16.55022586049862</v>
       </c>
       <c r="F11">
-        <v>0.8779756942034519</v>
+        <v>-0.4991958817269626</v>
       </c>
       <c r="G11">
-        <v>-7.936528559468864</v>
+        <v>-8.779496216025885</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.257810657496752</v>
       </c>
       <c r="E12">
-        <v>-16.21612492868412</v>
+        <v>-16.91159677787196</v>
       </c>
       <c r="F12">
-        <v>0.3862186990011365</v>
+        <v>-0.2407402818491001</v>
       </c>
       <c r="G12">
-        <v>-7.337211252622081</v>
+        <v>-8.338298655339878</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.885561832061106</v>
       </c>
       <c r="E13">
-        <v>-16.48181001034472</v>
+        <v>-17.90223320270403</v>
       </c>
       <c r="F13">
-        <v>1.15587639049463</v>
+        <v>-0.6731604916214839</v>
       </c>
       <c r="G13">
-        <v>-7.512849094989226</v>
+        <v>-8.111144295328589</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.466746045719385</v>
       </c>
       <c r="E14">
-        <v>-16.8959973161359</v>
+        <v>-18.44815621850745</v>
       </c>
       <c r="F14">
-        <v>1.254693994709389</v>
+        <v>-0.133987746282925</v>
       </c>
       <c r="G14">
-        <v>-6.751652569770464</v>
+        <v>-6.98479206175688</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.026066436355216</v>
       </c>
       <c r="E15">
-        <v>-16.82155100313835</v>
+        <v>-19.21068581774596</v>
       </c>
       <c r="F15">
-        <v>1.260813973081271</v>
+        <v>0.1619373963257676</v>
       </c>
       <c r="G15">
-        <v>-6.480735603550638</v>
+        <v>-7.027733588791511</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.591862458982087</v>
       </c>
       <c r="E16">
-        <v>-18.03693015239087</v>
+        <v>-20.42993575995323</v>
       </c>
       <c r="F16">
-        <v>1.949063029697241</v>
+        <v>0.2327884886546121</v>
       </c>
       <c r="G16">
-        <v>-5.650753790589813</v>
+        <v>-6.131613783104013</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.179983095840965</v>
       </c>
       <c r="E17">
-        <v>-19.91176450222232</v>
+        <v>-21.46997878670547</v>
       </c>
       <c r="F17">
-        <v>1.837949139755326</v>
+        <v>0.4513615115572897</v>
       </c>
       <c r="G17">
-        <v>-4.786722646671689</v>
+        <v>-5.484525071729039</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.800367780407353</v>
       </c>
       <c r="E18">
-        <v>-21.47623352296066</v>
+        <v>-21.92009137045641</v>
       </c>
       <c r="F18">
-        <v>1.752751552377397</v>
+        <v>0.4815795260440128</v>
       </c>
       <c r="G18">
-        <v>-4.02513712050885</v>
+        <v>-5.112898632907019</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.461281075560796</v>
       </c>
       <c r="E19">
-        <v>-21.34728046453606</v>
+        <v>-23.83139091571986</v>
       </c>
       <c r="F19">
-        <v>1.747483135695592</v>
+        <v>0.7024297309369862</v>
       </c>
       <c r="G19">
-        <v>-3.938972106023747</v>
+        <v>-4.798682467643579</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.158090299963705</v>
       </c>
       <c r="E20">
-        <v>-22.2287455764837</v>
+        <v>-23.2907964700462</v>
       </c>
       <c r="F20">
-        <v>1.83760122544615</v>
+        <v>1.059880205653807</v>
       </c>
       <c r="G20">
-        <v>-2.647778764341441</v>
+        <v>-4.407099497167088</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.895094040354203</v>
       </c>
       <c r="E21">
-        <v>-21.88728930741292</v>
+        <v>-24.30102359269749</v>
       </c>
       <c r="F21">
-        <v>2.594059710743437</v>
+        <v>1.427998395783879</v>
       </c>
       <c r="G21">
-        <v>-2.846816710478735</v>
+        <v>-4.265299515445362</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.666518256471905</v>
       </c>
       <c r="E22">
-        <v>-24.51926238818326</v>
+        <v>-24.56408799801213</v>
       </c>
       <c r="F22">
-        <v>2.254137490269854</v>
+        <v>1.31901672353677</v>
       </c>
       <c r="G22">
-        <v>-3.500210370041248</v>
+        <v>-4.049926140401471</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.472959850628702</v>
       </c>
       <c r="E23">
-        <v>-25.40065689553837</v>
+        <v>-24.73067745746233</v>
       </c>
       <c r="F23">
-        <v>3.053487182949293</v>
+        <v>1.46916991243782</v>
       </c>
       <c r="G23">
-        <v>-3.086355137457971</v>
+        <v>-3.898769250065194</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.314883858797945</v>
       </c>
       <c r="E24">
-        <v>-25.44915809738972</v>
+        <v>-25.11208346626664</v>
       </c>
       <c r="F24">
-        <v>2.98903688554188</v>
+        <v>1.103250209394777</v>
       </c>
       <c r="G24">
-        <v>-1.8092232661434</v>
+        <v>-4.514638677619636</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.188439852327444</v>
       </c>
       <c r="E25">
-        <v>-25.16499537854495</v>
+        <v>-25.98243873792035</v>
       </c>
       <c r="F25">
-        <v>2.729093537808589</v>
+        <v>1.359961267522344</v>
       </c>
       <c r="G25">
-        <v>-2.614536153462795</v>
+        <v>-3.627056006745079</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.098446163510719</v>
       </c>
       <c r="E26">
-        <v>-24.66648957643711</v>
+        <v>-24.98920655601026</v>
       </c>
       <c r="F26">
-        <v>3.191778150642253</v>
+        <v>1.181844051837589</v>
       </c>
       <c r="G26">
-        <v>-2.197179912382834</v>
+        <v>-3.930570729929545</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.039439730451718</v>
       </c>
       <c r="E27">
-        <v>-23.38401529823198</v>
+        <v>-25.78306798148328</v>
       </c>
       <c r="F27">
-        <v>2.208386758613237</v>
+        <v>1.386054840710529</v>
       </c>
       <c r="G27">
-        <v>-2.049056707261431</v>
+        <v>-3.66673671378541</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.012255077799945</v>
       </c>
       <c r="E28">
-        <v>-24.15355136497548</v>
+        <v>-26.092162427911</v>
       </c>
       <c r="F28">
-        <v>2.584962579925892</v>
+        <v>1.255421301289046</v>
       </c>
       <c r="G28">
-        <v>-1.731120230955655</v>
+        <v>-3.826877176259707</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.011301065280775</v>
       </c>
       <c r="E29">
-        <v>-24.43629783875848</v>
+        <v>-25.55162197398457</v>
       </c>
       <c r="F29">
-        <v>2.861450081427895</v>
+        <v>1.122930562150488</v>
       </c>
       <c r="G29">
-        <v>-2.264967895691091</v>
+        <v>-4.093692662726894</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.031630600337526</v>
       </c>
       <c r="E30">
-        <v>-25.11236588463672</v>
+        <v>-25.33236979493554</v>
       </c>
       <c r="F30">
-        <v>2.276692277913279</v>
+        <v>1.083115911302333</v>
       </c>
       <c r="G30">
-        <v>-1.638527563287231</v>
+        <v>-3.966254387000881</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.068516043922838</v>
       </c>
       <c r="E31">
-        <v>-24.0266250736774</v>
+        <v>-25.24100329900064</v>
       </c>
       <c r="F31">
-        <v>2.510662994099194</v>
+        <v>0.9534979503166828</v>
       </c>
       <c r="G31">
-        <v>-2.566289593419022</v>
+        <v>-4.013819542706374</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.112201989135745</v>
       </c>
       <c r="E32">
-        <v>-24.06721856116627</v>
+        <v>-25.33554700159904</v>
       </c>
       <c r="F32">
-        <v>2.592414573081477</v>
+        <v>0.8912246024438272</v>
       </c>
       <c r="G32">
-        <v>-2.756868727081109</v>
+        <v>-3.707513933554008</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.159446763897895</v>
       </c>
       <c r="E33">
-        <v>-22.6695342008104</v>
+        <v>-25.4606126542236</v>
       </c>
       <c r="F33">
-        <v>3.352827684359728</v>
+        <v>0.8369184922510972</v>
       </c>
       <c r="G33">
-        <v>-1.935679901903154</v>
+        <v>-3.63568973910789</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.202267982317428</v>
       </c>
       <c r="E34">
-        <v>-23.04973993154183</v>
+        <v>-25.28528483814596</v>
       </c>
       <c r="F34">
-        <v>2.266606076416792</v>
+        <v>1.332717920379074</v>
       </c>
       <c r="G34">
-        <v>-1.847710862905592</v>
+        <v>-3.604820295062567</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.239762319498845</v>
       </c>
       <c r="E35">
-        <v>-22.80886198112442</v>
+        <v>-24.78402130371843</v>
       </c>
       <c r="F35">
-        <v>2.362363691445609</v>
+        <v>1.319798702365013</v>
       </c>
       <c r="G35">
-        <v>-1.549143500721286</v>
+        <v>-3.530581161869669</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.270736572813928</v>
       </c>
       <c r="E36">
-        <v>-23.34997142500236</v>
+        <v>-23.79199355309254</v>
       </c>
       <c r="F36">
-        <v>2.716411232871729</v>
+        <v>1.531860757481686</v>
       </c>
       <c r="G36">
-        <v>-2.995558662068233</v>
+        <v>-3.820418194141293</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.295543510751693</v>
       </c>
       <c r="E37">
-        <v>-22.52732824504827</v>
+        <v>-23.84572364800184</v>
       </c>
       <c r="F37">
-        <v>2.091330160923639</v>
+        <v>1.457731815339964</v>
       </c>
       <c r="G37">
-        <v>-1.302208834315427</v>
+        <v>-3.996794877227725</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.320635157672524</v>
       </c>
       <c r="E38">
-        <v>-21.5195972024032</v>
+        <v>-24.18325513237066</v>
       </c>
       <c r="F38">
-        <v>2.755356097946945</v>
+        <v>1.41487871285834</v>
       </c>
       <c r="G38">
-        <v>-2.248663795719589</v>
+        <v>-3.784622275052539</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.34897254425662</v>
       </c>
       <c r="E39">
-        <v>-21.61818613283198</v>
+        <v>-23.08381287725072</v>
       </c>
       <c r="F39">
-        <v>2.885439601412968</v>
+        <v>1.627724403538062</v>
       </c>
       <c r="G39">
-        <v>-2.106451316352465</v>
+        <v>-3.846248901125768</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.389784570728834</v>
       </c>
       <c r="E40">
-        <v>-19.1767000894749</v>
+        <v>-22.17068783537392</v>
       </c>
       <c r="F40">
-        <v>2.411333458829505</v>
+        <v>1.715814649886567</v>
       </c>
       <c r="G40">
-        <v>-2.010871956871808</v>
+        <v>-3.93796958010076</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.445734875227936</v>
       </c>
       <c r="E41">
-        <v>-19.76983265840763</v>
+        <v>-21.7295461880846</v>
       </c>
       <c r="F41">
-        <v>3.474485034604474</v>
+        <v>1.814831062277998</v>
       </c>
       <c r="G41">
-        <v>-1.932327705848165</v>
+        <v>-3.489234799780208</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.520350446737364</v>
       </c>
       <c r="E42">
-        <v>-19.69753355566502</v>
+        <v>-21.39488872595257</v>
       </c>
       <c r="F42">
-        <v>3.251135645257255</v>
+        <v>1.768381188533418</v>
       </c>
       <c r="G42">
-        <v>-1.963186706915124</v>
+        <v>-3.157323007678203</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.61418402543055</v>
       </c>
       <c r="E43">
-        <v>-20.34757342617056</v>
+        <v>-21.69893286740929</v>
       </c>
       <c r="F43">
-        <v>3.115377825082055</v>
+        <v>1.715098940450548</v>
       </c>
       <c r="G43">
-        <v>-2.069749468890595</v>
+        <v>-3.843139504317752</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.721420436670172</v>
       </c>
       <c r="E44">
-        <v>-18.30222898539827</v>
+        <v>-20.33991075127625</v>
       </c>
       <c r="F44">
-        <v>3.090470474014679</v>
+        <v>2.139446709882651</v>
       </c>
       <c r="G44">
-        <v>-2.323315426557881</v>
+        <v>-3.838434942564566</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.839565012235577</v>
       </c>
       <c r="E45">
-        <v>-18.68848594502997</v>
+        <v>-20.45649139316419</v>
       </c>
       <c r="F45">
-        <v>3.080429004357944</v>
+        <v>2.05015036059567</v>
       </c>
       <c r="G45">
-        <v>-2.037509383934937</v>
+        <v>-4.062888487296348</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.958246844697783</v>
       </c>
       <c r="E46">
-        <v>-17.53849910808687</v>
+        <v>-19.35883917212525</v>
       </c>
       <c r="F46">
-        <v>2.684474356024197</v>
+        <v>1.882738965224695</v>
       </c>
       <c r="G46">
-        <v>-2.522468245457185</v>
+        <v>-4.044955282699991</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.072105534404345</v>
       </c>
       <c r="E47">
-        <v>-16.89351369576365</v>
+        <v>-19.4326832694807</v>
       </c>
       <c r="F47">
-        <v>3.048838385084782</v>
+        <v>2.114693435152196</v>
       </c>
       <c r="G47">
-        <v>-2.370883193007966</v>
+        <v>-3.699629484888846</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.173185619884283</v>
       </c>
       <c r="E48">
-        <v>-15.32864596673813</v>
+        <v>-18.70579652983186</v>
       </c>
       <c r="F48">
-        <v>2.790777088090652</v>
+        <v>2.174880953904803</v>
       </c>
       <c r="G48">
-        <v>-1.642490673576541</v>
+        <v>-3.717233735666723</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.25379828383321</v>
       </c>
       <c r="E49">
-        <v>-16.43005269081471</v>
+        <v>-18.15736497438825</v>
       </c>
       <c r="F49">
-        <v>2.922366563494965</v>
+        <v>1.819713459750098</v>
       </c>
       <c r="G49">
-        <v>-2.08894366312446</v>
+        <v>-3.828861342148953</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.312299185273309</v>
       </c>
       <c r="E50">
-        <v>-16.45539558631882</v>
+        <v>-17.32202542741416</v>
       </c>
       <c r="F50">
-        <v>3.19069133260978</v>
+        <v>1.854397202905313</v>
       </c>
       <c r="G50">
-        <v>-1.743341126386656</v>
+        <v>-3.802769560705367</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.342731643890045</v>
       </c>
       <c r="E51">
-        <v>-14.98566131589981</v>
+        <v>-16.72139215882878</v>
       </c>
       <c r="F51">
-        <v>2.479072374826031</v>
+        <v>1.900565431732941</v>
       </c>
       <c r="G51">
-        <v>-3.616660021783265</v>
+        <v>-4.155071268063967</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.34727197956974</v>
       </c>
       <c r="E52">
-        <v>-14.36457763475098</v>
+        <v>-16.74864137833098</v>
       </c>
       <c r="F52">
-        <v>2.612442840146363</v>
+        <v>1.978456818618178</v>
       </c>
       <c r="G52">
-        <v>-3.169724044485991</v>
+        <v>-3.369730576866589</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.325489024851602</v>
       </c>
       <c r="E53">
-        <v>-14.29092873832779</v>
+        <v>-15.99531944859961</v>
       </c>
       <c r="F53">
-        <v>2.317756106804856</v>
+        <v>1.913622158735867</v>
       </c>
       <c r="G53">
-        <v>-3.003649359556093</v>
+        <v>-3.505003697110533</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.281371872975774</v>
       </c>
       <c r="E54">
-        <v>-14.27337726726907</v>
+        <v>-15.09697568582787</v>
       </c>
       <c r="F54">
-        <v>2.591342665662254</v>
+        <v>1.850442576924348</v>
       </c>
       <c r="G54">
-        <v>-2.272418960754128</v>
+        <v>-3.665896054027071</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.222642395888897</v>
       </c>
       <c r="E55">
-        <v>-12.83714279939614</v>
+        <v>-14.99869409303713</v>
       </c>
       <c r="F55">
-        <v>2.751141364601501</v>
+        <v>2.100513441951074</v>
       </c>
       <c r="G55">
-        <v>-3.481731519825349</v>
+        <v>-3.705631586703815</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.154437681362698</v>
       </c>
       <c r="E56">
-        <v>-13.24652899289581</v>
+        <v>-14.42643556422298</v>
       </c>
       <c r="F56">
-        <v>2.308562885368587</v>
+        <v>1.650209608319652</v>
       </c>
       <c r="G56">
-        <v>-3.755434150523892</v>
+        <v>-3.888903246255377</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.088821403355817</v>
       </c>
       <c r="E57">
-        <v>-12.15340377220094</v>
+        <v>-14.73982858437189</v>
       </c>
       <c r="F57">
-        <v>2.604949428620639</v>
+        <v>1.957896739680695</v>
       </c>
       <c r="G57">
-        <v>-2.561835663146582</v>
+        <v>-3.935251794981411</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.03016834583989</v>
       </c>
       <c r="E58">
-        <v>-10.76535486211867</v>
+        <v>-13.89852917914667</v>
       </c>
       <c r="F58">
-        <v>2.08923273465975</v>
+        <v>1.769999818438488</v>
       </c>
       <c r="G58">
-        <v>-3.231551697892736</v>
+        <v>-3.948159316239875</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.98642170473012</v>
       </c>
       <c r="E59">
-        <v>-10.4647828053295</v>
+        <v>-14.37205341513567</v>
       </c>
       <c r="F59">
-        <v>2.484065773530107</v>
+        <v>1.73471468054884</v>
       </c>
       <c r="G59">
-        <v>-2.629957821762501</v>
+        <v>-4.166605537667506</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.961116451894489</v>
       </c>
       <c r="E60">
-        <v>-10.72907240798497</v>
+        <v>-13.90050610773729</v>
       </c>
       <c r="F60">
-        <v>2.242083087824315</v>
+        <v>1.86982140394544</v>
       </c>
       <c r="G60">
-        <v>-2.529916699775631</v>
+        <v>-4.463802258941477</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.952891109047146</v>
       </c>
       <c r="E61">
-        <v>-10.53123003331543</v>
+        <v>-13.50190580404819</v>
       </c>
       <c r="F61">
-        <v>2.497387578101928</v>
+        <v>1.865389638340462</v>
       </c>
       <c r="G61">
-        <v>-3.628719051049618</v>
+        <v>-4.240617536080976</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.964194802720516</v>
       </c>
       <c r="E62">
-        <v>-9.981149652975867</v>
+        <v>-12.44770447988961</v>
       </c>
       <c r="F62">
-        <v>2.356671150653571</v>
+        <v>1.686613042203079</v>
       </c>
       <c r="G62">
-        <v>-2.608236426764439</v>
+        <v>-4.613982730800679</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.988543901888592</v>
       </c>
       <c r="E63">
-        <v>-9.246579472376093</v>
+        <v>-12.90814610020541</v>
       </c>
       <c r="F63">
-        <v>2.278710180906498</v>
+        <v>1.965617123874786</v>
       </c>
       <c r="G63">
-        <v>-3.090440952743063</v>
+        <v>-4.449565868686137</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.025240038779919</v>
       </c>
       <c r="E64">
-        <v>-10.57713963130009</v>
+        <v>-12.46725364559558</v>
       </c>
       <c r="F64">
-        <v>1.56851767179037</v>
+        <v>1.657202685934085</v>
       </c>
       <c r="G64">
-        <v>-3.781217864105727</v>
+        <v>-4.468109987516815</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.067824269378442</v>
       </c>
       <c r="E65">
-        <v>-9.914415853408522</v>
+        <v>-11.83317456621136</v>
       </c>
       <c r="F65">
-        <v>1.752337368675997</v>
+        <v>1.464617205192034</v>
       </c>
       <c r="G65">
-        <v>-4.819223806086458</v>
+        <v>-4.752730752095394</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.109306515123106</v>
       </c>
       <c r="E66">
-        <v>-9.008783204761709</v>
+        <v>-12.41312484239909</v>
       </c>
       <c r="F66">
-        <v>2.125763737123209</v>
+        <v>1.598201389302288</v>
       </c>
       <c r="G66">
-        <v>-3.893855828744718</v>
+        <v>-4.433924897840777</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.145092076687873</v>
       </c>
       <c r="E67">
-        <v>-8.606320414540525</v>
+        <v>-11.55439025603224</v>
       </c>
       <c r="F67">
-        <v>1.898347063828244</v>
+        <v>1.833051831669976</v>
       </c>
       <c r="G67">
-        <v>-3.669629418792363</v>
+        <v>-4.718493447527535</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.165728238952549</v>
       </c>
       <c r="E68">
-        <v>-9.710833740688077</v>
+        <v>-12.30190599633151</v>
       </c>
       <c r="F68">
-        <v>2.121086774767003</v>
+        <v>1.68102984590821</v>
       </c>
       <c r="G68">
-        <v>-3.288058653822792</v>
+        <v>-4.627978932553637</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.169294115957098</v>
       </c>
       <c r="E69">
-        <v>-8.776419337560203</v>
+        <v>-12.08608436983679</v>
       </c>
       <c r="F69">
-        <v>2.133230640892044</v>
+        <v>1.587541957563064</v>
       </c>
       <c r="G69">
-        <v>-4.301445274309325</v>
+        <v>-4.74170035619794</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.149891376656488</v>
       </c>
       <c r="E70">
-        <v>-9.191877526016775</v>
+        <v>-11.746098337575</v>
       </c>
       <c r="F70">
-        <v>2.155561769336713</v>
+        <v>1.670844240323387</v>
       </c>
       <c r="G70">
-        <v>-4.205312436975351</v>
+        <v>-4.78832042236145</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.106433992597769</v>
       </c>
       <c r="E71">
-        <v>-9.504057808458837</v>
+        <v>-11.31457552771399</v>
       </c>
       <c r="F71">
-        <v>1.995484738950125</v>
+        <v>1.686830074462612</v>
       </c>
       <c r="G71">
-        <v>-4.54147713201628</v>
+        <v>-4.561519818242257</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.03900885060955</v>
       </c>
       <c r="E72">
-        <v>-10.19661410329665</v>
+        <v>-11.32276981365788</v>
       </c>
       <c r="F72">
-        <v>1.925126525225946</v>
+        <v>1.614796901849973</v>
       </c>
       <c r="G72">
-        <v>-4.028215188381773</v>
+        <v>-4.836522599747175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.945666308709075</v>
       </c>
       <c r="E73">
-        <v>-9.157451557345272</v>
+        <v>-11.52977001929866</v>
       </c>
       <c r="F73">
-        <v>2.162134036310524</v>
+        <v>1.323465056489804</v>
       </c>
       <c r="G73">
-        <v>-3.735482840358605</v>
+        <v>-4.487157980053578</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.830350269758341</v>
       </c>
       <c r="E74">
-        <v>-9.224318259675011</v>
+        <v>-11.38631810013908</v>
       </c>
       <c r="F74">
-        <v>1.515184064928527</v>
+        <v>1.444933538966712</v>
       </c>
       <c r="G74">
-        <v>-3.750150003471479</v>
+        <v>-4.669082495396125</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.692496124707852</v>
       </c>
       <c r="E75">
-        <v>-8.635289063531204</v>
+        <v>-12.08693162494706</v>
       </c>
       <c r="F75">
-        <v>2.52583868491848</v>
+        <v>1.202493594454575</v>
       </c>
       <c r="G75">
-        <v>-3.114504185639354</v>
+        <v>-4.424565378481637</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.536283038081717</v>
       </c>
       <c r="E76">
-        <v>-11.67394875044008</v>
+        <v>-11.9635895550223</v>
       </c>
       <c r="F76">
-        <v>1.908181441634279</v>
+        <v>1.368629304025238</v>
       </c>
       <c r="G76">
-        <v>-3.478491585787777</v>
+        <v>-4.189637526450308</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.364344775597919</v>
       </c>
       <c r="E77">
-        <v>-9.593231408814232</v>
+        <v>-11.86382526578859</v>
       </c>
       <c r="F77">
-        <v>1.074439591125411</v>
+        <v>1.330764630043273</v>
       </c>
       <c r="G77">
-        <v>-3.891031003097134</v>
+        <v>-3.930518515037722</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.178589037535497</v>
       </c>
       <c r="E78">
-        <v>-9.051719103437787</v>
+        <v>-11.83523040581715</v>
       </c>
       <c r="F78">
-        <v>0.7012749867774837</v>
+        <v>0.9643628171718011</v>
       </c>
       <c r="G78">
-        <v>-2.074819534886537</v>
+        <v>-3.530260040284963</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.985549867924391</v>
       </c>
       <c r="E79">
-        <v>-10.38855891788492</v>
+        <v>-12.63325334903765</v>
       </c>
       <c r="F79">
-        <v>1.117995149164609</v>
+        <v>1.11126383564946</v>
       </c>
       <c r="G79">
-        <v>-3.063127342830835</v>
+        <v>-3.987338760318712</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.78784248349441</v>
       </c>
       <c r="E80">
-        <v>-10.83711820060038</v>
+        <v>-14.00384631192167</v>
       </c>
       <c r="F80">
-        <v>0.9273347942666632</v>
+        <v>0.9225103825127589</v>
       </c>
       <c r="G80">
-        <v>-2.691626219749188</v>
+        <v>-3.969110541583559</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.594670996396484</v>
       </c>
       <c r="E81">
-        <v>-11.74449935121494</v>
+        <v>-13.72423551268892</v>
       </c>
       <c r="F81">
-        <v>0.3439785883975842</v>
+        <v>0.8822069948969518</v>
       </c>
       <c r="G81">
-        <v>-1.680732860347169</v>
+        <v>-3.462004733694897</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.41218215350265</v>
       </c>
       <c r="E82">
-        <v>-14.19881466435442</v>
+        <v>-14.1128307302965</v>
       </c>
       <c r="F82">
-        <v>0.8076572421146074</v>
+        <v>0.7131280959441418</v>
       </c>
       <c r="G82">
-        <v>-3.918300230351313</v>
+        <v>-3.34515824877503</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.248920172793561</v>
       </c>
       <c r="E83">
-        <v>-11.84475371938498</v>
+        <v>-14.59656355972193</v>
       </c>
       <c r="F83">
-        <v>0.7284537212633355</v>
+        <v>0.8036081822497234</v>
       </c>
       <c r="G83">
-        <v>-2.988397389654809</v>
+        <v>-3.794947769910392</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.113662664454158</v>
       </c>
       <c r="E84">
-        <v>-13.34406716085941</v>
+        <v>-15.57901815824409</v>
       </c>
       <c r="F84">
-        <v>0.6546934026158591</v>
+        <v>0.8687393976622374</v>
       </c>
       <c r="G84">
-        <v>-2.821275796143874</v>
+        <v>-3.33010208471808</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.011114785751791</v>
       </c>
       <c r="E85">
-        <v>-15.08658019788182</v>
+        <v>-16.8971186831936</v>
       </c>
       <c r="F85">
-        <v>0.4748680933465312</v>
+        <v>0.3537682343638687</v>
       </c>
       <c r="G85">
-        <v>-1.987732927560771</v>
+        <v>-3.260703271997107</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9494186072757196</v>
       </c>
       <c r="E86">
-        <v>-16.98967299756741</v>
+        <v>-17.10041007112131</v>
       </c>
       <c r="F86">
-        <v>0.2000605209374064</v>
+        <v>0.2401692422135557</v>
       </c>
       <c r="G86">
-        <v>-1.927469110164103</v>
+        <v>-3.795122689797997</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9293025786963237</v>
       </c>
       <c r="E87">
-        <v>-17.50035601527965</v>
+        <v>-17.95248705973446</v>
       </c>
       <c r="F87">
-        <v>0.3742082000279465</v>
+        <v>-0.2515877529887596</v>
       </c>
       <c r="G87">
-        <v>-2.456165775821272</v>
+        <v>-3.501591453929947</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.9541684018382166</v>
       </c>
       <c r="E88">
-        <v>-17.66675027379758</v>
+        <v>-20.12689254242579</v>
       </c>
       <c r="F88">
-        <v>-0.001086136912577904</v>
+        <v>-0.1505095341317611</v>
       </c>
       <c r="G88">
-        <v>-2.210821052871401</v>
+        <v>-3.29112627871735</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.022021770701957</v>
       </c>
       <c r="E89">
-        <v>-20.88274377785399</v>
+        <v>-21.75495968818123</v>
       </c>
       <c r="F89">
-        <v>0.1055123223166765</v>
+        <v>-0.1915377432250178</v>
       </c>
       <c r="G89">
-        <v>-2.647770932107667</v>
+        <v>-3.235533083394184</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.129537355754246</v>
       </c>
       <c r="E90">
-        <v>-20.70748656636887</v>
+        <v>-23.53409158945466</v>
       </c>
       <c r="F90">
-        <v>0.3321553004574268</v>
+        <v>-0.4236595433678841</v>
       </c>
       <c r="G90">
-        <v>-1.489608081065538</v>
+        <v>-3.212391443338555</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.273799238778511</v>
       </c>
       <c r="E91">
-        <v>-23.71611853539924</v>
+        <v>-24.28445643272275</v>
       </c>
       <c r="F91">
-        <v>0.2029656054190243</v>
+        <v>-0.3872784754043326</v>
       </c>
       <c r="G91">
-        <v>-2.163879865123184</v>
+        <v>-3.610101831370389</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.446156766166853</v>
       </c>
       <c r="E92">
-        <v>-26.03388871981233</v>
+        <v>-26.45283560578176</v>
       </c>
       <c r="F92">
-        <v>-0.45798543180509</v>
+        <v>-0.8597353384888222</v>
       </c>
       <c r="G92">
-        <v>-2.258568960698272</v>
+        <v>-3.562079795361451</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.642146182889339</v>
       </c>
       <c r="E93">
-        <v>-27.79807736673903</v>
+        <v>-29.02095929224985</v>
       </c>
       <c r="F93">
-        <v>-0.1517794213602528</v>
+        <v>-1.091123205112808</v>
       </c>
       <c r="G93">
-        <v>-2.541202948643014</v>
+        <v>-3.676660153976231</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.850645561442621</v>
       </c>
       <c r="E94">
-        <v>-30.60457669380131</v>
+        <v>-30.04878564789011</v>
       </c>
       <c r="F94">
-        <v>-0.2090328627721434</v>
+        <v>-0.9844228566930094</v>
       </c>
       <c r="G94">
-        <v>-2.848847869770621</v>
+        <v>-3.462537325591484</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.064934788414628</v>
       </c>
       <c r="E95">
-        <v>-32.47304832388313</v>
+        <v>-32.41634452966525</v>
       </c>
       <c r="F95">
-        <v>-0.5353375515111051</v>
+        <v>-0.9368944485899849</v>
       </c>
       <c r="G95">
-        <v>-2.946147709936823</v>
+        <v>-3.932416526355462</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.275602163405159</v>
       </c>
       <c r="E96">
-        <v>-35.32339933271862</v>
+        <v>-34.54699800765517</v>
       </c>
       <c r="F96">
-        <v>-1.178018945666476</v>
+        <v>-1.263165174265432</v>
       </c>
       <c r="G96">
-        <v>-2.110923521837043</v>
+        <v>-3.506541425674699</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.473725983798211</v>
       </c>
       <c r="E97">
-        <v>-36.40497031950782</v>
+        <v>-37.0433168235283</v>
       </c>
       <c r="F97">
-        <v>-1.105757143650664</v>
+        <v>-1.409686800472608</v>
       </c>
       <c r="G97">
-        <v>-3.216626071065341</v>
+        <v>-3.748353811192793</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.652454030844341</v>
       </c>
       <c r="E98">
-        <v>-39.66010576369507</v>
+        <v>-39.14306002623319</v>
       </c>
       <c r="F98">
-        <v>-0.9857242218828075</v>
+        <v>-1.674807444473396</v>
       </c>
       <c r="G98">
-        <v>-2.678820517529778</v>
+        <v>-4.244726848067389</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.802672831772017</v>
       </c>
       <c r="E99">
-        <v>-42.42895623009779</v>
+        <v>-42.02720363901315</v>
       </c>
       <c r="F99">
-        <v>-1.293282127929013</v>
+        <v>-1.789141198509992</v>
       </c>
       <c r="G99">
-        <v>-3.935136922219402</v>
+        <v>-4.135083407474404</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.916567351723984</v>
       </c>
       <c r="E100">
-        <v>-43.51886478862158</v>
+        <v>-44.32245095841169</v>
       </c>
       <c r="F100">
-        <v>-1.094549332690787</v>
+        <v>-1.696760837382388</v>
       </c>
       <c r="G100">
-        <v>-3.335584648359418</v>
+        <v>-4.195417714975032</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.987238330699369</v>
       </c>
       <c r="E101">
-        <v>-46.1751850324809</v>
+        <v>-47.72971749512459</v>
       </c>
       <c r="F101">
-        <v>-1.136424961637108</v>
+        <v>-2.268322748170408</v>
       </c>
       <c r="G101">
-        <v>-2.926248614663357</v>
+        <v>-3.707083160696474</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.000393739084207</v>
       </c>
       <c r="E102">
-        <v>-50.31402105461138</v>
+        <v>-50.37810095214216</v>
       </c>
       <c r="F102">
-        <v>-1.428637361546453</v>
+        <v>-2.31441228209477</v>
       </c>
       <c r="G102">
-        <v>-3.809434791646479</v>
+        <v>-4.344431184002005</v>
       </c>
     </row>
   </sheetData>
